--- a/rtos-api-analysis/results/memory/RT-Thread_memory_and_coverage_analysis.xlsx
+++ b/rtos-api-analysis/results/memory/RT-Thread_memory_and_coverage_analysis.xlsx
@@ -653,7 +653,7 @@
         <v>1145</v>
       </c>
       <c r="C14" t="n">
-        <v>7.18</v>
+        <v>7.14</v>
       </c>
       <c r="D14" t="n">
         <v>0.13</v>
@@ -829,7 +829,7 @@
         <v>5074</v>
       </c>
       <c r="C25" t="n">
-        <v>12.52</v>
+        <v>12.53</v>
       </c>
       <c r="D25" t="n">
         <v>0.08</v>
@@ -861,7 +861,7 @@
         <v>1509</v>
       </c>
       <c r="C27" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="D27" t="n">
         <v>0.03</v>
@@ -973,7 +973,7 @@
         <v>2100</v>
       </c>
       <c r="C34" t="n">
-        <v>11.75</v>
+        <v>11.76</v>
       </c>
       <c r="D34" t="n">
         <v>0.04</v>
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>35883</v>
+        <v>35919</v>
       </c>
       <c r="C35" t="n">
-        <v>9.880000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D35" t="n">
         <v>0.34</v>
@@ -1037,7 +1037,7 @@
         <v>2389</v>
       </c>
       <c r="C38" t="n">
-        <v>8.4</v>
+        <v>8.41</v>
       </c>
       <c r="D38" t="n">
         <v>0.21</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11218</v>
+        <v>11150</v>
       </c>
       <c r="C40" t="n">
-        <v>9.51</v>
+        <v>9.58</v>
       </c>
       <c r="D40" t="n">
         <v>0.25</v>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>361</v>
+        <v>2636</v>
       </c>
       <c r="C42" t="n">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="D42" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="43">
@@ -1181,7 +1181,7 @@
         <v>6818</v>
       </c>
       <c r="C47" t="n">
-        <v>12.55</v>
+        <v>12.56</v>
       </c>
       <c r="D47" t="n">
         <v>0.08</v>
@@ -1213,7 +1213,7 @@
         <v>1449</v>
       </c>
       <c r="C49" t="n">
-        <v>15.1</v>
+        <v>15.11</v>
       </c>
       <c r="D49" t="n">
         <v>0.02</v>
@@ -1229,7 +1229,7 @@
         <v>197</v>
       </c>
       <c r="C50" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="D50" t="n">
         <v>0.76</v>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>566</v>
+        <v>4162</v>
       </c>
       <c r="C51" t="n">
-        <v>7.48</v>
+        <v>7.5</v>
       </c>
       <c r="D51" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="52">
@@ -1325,7 +1325,7 @@
         <v>10960</v>
       </c>
       <c r="C56" t="n">
-        <v>10.68</v>
+        <v>10.7</v>
       </c>
       <c r="D56" t="n">
         <v>0.2</v>
@@ -1373,7 +1373,7 @@
         <v>13364</v>
       </c>
       <c r="C59" t="n">
-        <v>10.64</v>
+        <v>10.73</v>
       </c>
       <c r="D59" t="n">
         <v>0.13</v>
@@ -1469,7 +1469,7 @@
         <v>540138</v>
       </c>
       <c r="C65" t="n">
-        <v>18.94</v>
+        <v>19.75</v>
       </c>
       <c r="D65" t="n">
         <v>0.21</v>
@@ -1485,7 +1485,7 @@
         <v>13364</v>
       </c>
       <c r="C66" t="n">
-        <v>10.65</v>
+        <v>10.73</v>
       </c>
       <c r="D66" t="n">
         <v>0.13</v>
@@ -1565,7 +1565,7 @@
         <v>4099</v>
       </c>
       <c r="C71" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D71" t="n">
         <v>0.26</v>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1130</v>
+        <v>12182</v>
       </c>
       <c r="C72" t="n">
-        <v>7.48</v>
+        <v>7.49</v>
       </c>
       <c r="D72" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="73">
@@ -1677,7 +1677,7 @@
         <v>19</v>
       </c>
       <c r="C78" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         <v>13364</v>
       </c>
       <c r="C80" t="n">
-        <v>10.66</v>
+        <v>10.84</v>
       </c>
       <c r="D80" t="n">
         <v>0.13</v>
@@ -1741,7 +1741,7 @@
         <v>18</v>
       </c>
       <c r="C82" t="n">
-        <v>5.65</v>
+        <v>5.66</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -1757,7 +1757,7 @@
         <v>7263</v>
       </c>
       <c r="C83" t="n">
-        <v>11.07</v>
+        <v>11.08</v>
       </c>
       <c r="D83" t="n">
         <v>0.05</v>
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="C87" t="n">
-        <v>6.88</v>
+        <v>6.93</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="88">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>321</v>
+        <v>610</v>
       </c>
       <c r="C90" t="n">
-        <v>7.06</v>
+        <v>7.02</v>
       </c>
       <c r="D90" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="91">
@@ -1901,7 +1901,7 @@
         <v>1562</v>
       </c>
       <c r="C92" t="n">
-        <v>16.15</v>
+        <v>16.16</v>
       </c>
       <c r="D92" t="n">
         <v>0.02</v>
@@ -1949,7 +1949,7 @@
         <v>4148</v>
       </c>
       <c r="C95" t="n">
-        <v>10.4</v>
+        <v>10.43</v>
       </c>
       <c r="D95" t="n">
         <v>0.11</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>55595</v>
+        <v>51797</v>
       </c>
       <c r="C98" t="n">
-        <v>9.9</v>
+        <v>9.82</v>
       </c>
       <c r="D98" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="99">
@@ -2106,13 +2106,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>278</v>
+        <v>516</v>
       </c>
       <c r="C105" t="n">
-        <v>7.02</v>
+        <v>6.98</v>
       </c>
       <c r="D105" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="106">
@@ -2138,13 +2138,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>512</v>
+        <v>4580</v>
       </c>
       <c r="C107" t="n">
-        <v>7.45</v>
+        <v>7.47</v>
       </c>
       <c r="D107" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="108">
@@ -2189,7 +2189,7 @@
         <v>19</v>
       </c>
       <c r="C110" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
@@ -2269,7 +2269,7 @@
         <v>1163</v>
       </c>
       <c r="C115" t="n">
-        <v>13.83</v>
+        <v>13.84</v>
       </c>
       <c r="D115" t="n">
         <v>0.02</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>143507</v>
+        <v>141180</v>
       </c>
       <c r="C116" t="n">
-        <v>11.11</v>
+        <v>11.15</v>
       </c>
       <c r="D116" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="117">
@@ -2330,13 +2330,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>346</v>
+        <v>610</v>
       </c>
       <c r="C119" t="n">
-        <v>6.96</v>
+        <v>6.94</v>
       </c>
       <c r="D119" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="120">
@@ -2445,7 +2445,7 @@
         <v>1305</v>
       </c>
       <c r="C126" t="n">
-        <v>8.380000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D126" t="n">
         <v>0.22</v>
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>146195</v>
+        <v>145382</v>
       </c>
       <c r="C127" t="n">
-        <v>14.65</v>
+        <v>14.76</v>
       </c>
       <c r="D127" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="128">
@@ -2493,7 +2493,7 @@
         <v>895</v>
       </c>
       <c r="C129" t="n">
-        <v>15.98</v>
+        <v>15.99</v>
       </c>
       <c r="D129" t="n">
         <v>0.02</v>
@@ -2573,7 +2573,7 @@
         <v>2401</v>
       </c>
       <c r="C134" t="n">
-        <v>8.41</v>
+        <v>8.43</v>
       </c>
       <c r="D134" t="n">
         <v>0.22</v>
@@ -2685,7 +2685,7 @@
         <v>4159</v>
       </c>
       <c r="C141" t="n">
-        <v>12</v>
+        <v>12.01</v>
       </c>
       <c r="D141" t="n">
         <v>0.04</v>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>325</v>
+        <v>525</v>
       </c>
       <c r="C145" t="n">
-        <v>7</v>
+        <v>6.97</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="146">
@@ -2813,7 +2813,7 @@
         <v>26</v>
       </c>
       <c r="C149" t="n">
-        <v>5.66</v>
+        <v>5.67</v>
       </c>
       <c r="D149" t="n">
         <v>1</v>
@@ -2941,7 +2941,7 @@
         <v>4607</v>
       </c>
       <c r="C157" t="n">
-        <v>9.720000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="D157" t="n">
         <v>0.15</v>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>6500431</v>
+        <v>2792466</v>
       </c>
       <c r="C159" t="n">
-        <v>88.81999999999999</v>
+        <v>52.77</v>
       </c>
       <c r="D159" t="n">
         <v>0.08</v>
@@ -3021,7 +3021,7 @@
         <v>1663</v>
       </c>
       <c r="C162" t="n">
-        <v>10.92</v>
+        <v>10.93</v>
       </c>
       <c r="D162" t="n">
         <v>0.05</v>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>104657</v>
+        <v>100260</v>
       </c>
       <c r="C163" t="n">
-        <v>21.79</v>
+        <v>21.81</v>
       </c>
       <c r="D163" t="n">
         <v>0.06</v>
@@ -3069,7 +3069,7 @@
         <v>13364</v>
       </c>
       <c r="C165" t="n">
-        <v>10.64</v>
+        <v>10.73</v>
       </c>
       <c r="D165" t="n">
         <v>0.13</v>
@@ -3194,13 +3194,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1869</v>
+        <v>181265</v>
       </c>
       <c r="C173" t="n">
-        <v>14.73</v>
+        <v>21.53</v>
       </c>
       <c r="D173" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="174">
@@ -3213,7 +3213,7 @@
         <v>9149</v>
       </c>
       <c r="C174" t="n">
-        <v>13.62</v>
+        <v>13.48</v>
       </c>
       <c r="D174" t="n">
         <v>0.03</v>
@@ -3389,7 +3389,7 @@
         <v>4803</v>
       </c>
       <c r="C185" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="D185" t="n">
         <v>0.16</v>
@@ -3469,7 +3469,7 @@
         <v>13364</v>
       </c>
       <c r="C190" t="n">
-        <v>10.65</v>
+        <v>10.73</v>
       </c>
       <c r="D190" t="n">
         <v>0.13</v>
@@ -3533,7 +3533,7 @@
         <v>154</v>
       </c>
       <c r="C194" t="n">
-        <v>11.28</v>
+        <v>11.29</v>
       </c>
       <c r="D194" t="n">
         <v>0.01</v>
@@ -3549,7 +3549,7 @@
         <v>113</v>
       </c>
       <c r="C195" t="n">
-        <v>9.52</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="D195" t="n">
         <v>0.01</v>
@@ -3581,7 +3581,7 @@
         <v>193</v>
       </c>
       <c r="C197" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="D197" t="n">
         <v>0.76</v>
@@ -3629,7 +3629,7 @@
         <v>13364</v>
       </c>
       <c r="C200" t="n">
-        <v>10.64</v>
+        <v>10.73</v>
       </c>
       <c r="D200" t="n">
         <v>0.13</v>
@@ -3645,7 +3645,7 @@
         <v>26978</v>
       </c>
       <c r="C201" t="n">
-        <v>6.93</v>
+        <v>7.1</v>
       </c>
       <c r="D201" t="n">
         <v>0.92</v>
@@ -3693,7 +3693,7 @@
         <v>13702</v>
       </c>
       <c r="C204" t="n">
-        <v>9.65</v>
+        <v>9.6</v>
       </c>
       <c r="D204" t="n">
         <v>0.26</v>
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>634</v>
+        <v>4766</v>
       </c>
       <c r="C205" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="D205" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="206">
@@ -3799,28 +3799,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1915.98</v>
+        <v>1888.51</v>
       </c>
       <c r="B2" t="n">
-        <v>9.3462</v>
+        <v>9.212199999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>88.81999999999999</v>
+        <v>52.77</v>
       </c>
       <c r="D2" t="n">
         <v>5.63</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3887</v>
+        <v>4.445</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3052</v>
+        <v>0.3071</v>
       </c>
       <c r="G2" t="n">
         <v>0.1317</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3415</v>
+        <v>0.3366</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>

--- a/rtos-api-analysis/results/memory/RT-Thread_memory_and_coverage_analysis.xlsx
+++ b/rtos-api-analysis/results/memory/RT-Thread_memory_and_coverage_analysis.xlsx
@@ -685,7 +685,7 @@
         <v>1990</v>
       </c>
       <c r="C16" t="n">
-        <v>6.62</v>
+        <v>6.61</v>
       </c>
       <c r="D16" t="n">
         <v>0.29</v>
@@ -733,7 +733,7 @@
         <v>758</v>
       </c>
       <c r="C19" t="n">
-        <v>6.94</v>
+        <v>6.93</v>
       </c>
       <c r="D19" t="n">
         <v>0.15</v>
@@ -765,7 +765,7 @@
         <v>2852</v>
       </c>
       <c r="C21" t="n">
-        <v>11.94</v>
+        <v>11.93</v>
       </c>
       <c r="D21" t="n">
         <v>0.04</v>
@@ -829,7 +829,7 @@
         <v>5074</v>
       </c>
       <c r="C25" t="n">
-        <v>12.53</v>
+        <v>12.52</v>
       </c>
       <c r="D25" t="n">
         <v>0.08</v>
@@ -861,7 +861,7 @@
         <v>1509</v>
       </c>
       <c r="C27" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="D27" t="n">
         <v>0.03</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C32" t="n">
-        <v>15.14</v>
+        <v>15.13</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>2100</v>
       </c>
       <c r="C34" t="n">
-        <v>11.76</v>
+        <v>11.75</v>
       </c>
       <c r="D34" t="n">
         <v>0.04</v>
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>35919</v>
+        <v>35883</v>
       </c>
       <c r="C35" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="D35" t="n">
         <v>0.34</v>
@@ -1037,7 +1037,7 @@
         <v>2389</v>
       </c>
       <c r="C38" t="n">
-        <v>8.41</v>
+        <v>8.4</v>
       </c>
       <c r="D38" t="n">
         <v>0.21</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11150</v>
+        <v>13117</v>
       </c>
       <c r="C40" t="n">
-        <v>9.58</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="D40" t="n">
         <v>0.25</v>
@@ -1101,7 +1101,7 @@
         <v>2636</v>
       </c>
       <c r="C42" t="n">
-        <v>7.05</v>
+        <v>7.04</v>
       </c>
       <c r="D42" t="n">
         <v>0.14</v>
@@ -1181,7 +1181,7 @@
         <v>6818</v>
       </c>
       <c r="C47" t="n">
-        <v>12.56</v>
+        <v>12.55</v>
       </c>
       <c r="D47" t="n">
         <v>0.08</v>
@@ -1213,7 +1213,7 @@
         <v>1449</v>
       </c>
       <c r="C49" t="n">
-        <v>15.11</v>
+        <v>15.1</v>
       </c>
       <c r="D49" t="n">
         <v>0.02</v>
@@ -1229,7 +1229,7 @@
         <v>197</v>
       </c>
       <c r="C50" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="D50" t="n">
         <v>0.76</v>
@@ -1245,7 +1245,7 @@
         <v>4162</v>
       </c>
       <c r="C51" t="n">
-        <v>7.5</v>
+        <v>7.49</v>
       </c>
       <c r="D51" t="n">
         <v>0.16</v>
@@ -1277,7 +1277,7 @@
         <v>1160</v>
       </c>
       <c r="C53" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="D53" t="n">
         <v>0.04</v>
@@ -1293,7 +1293,7 @@
         <v>1419</v>
       </c>
       <c r="C54" t="n">
-        <v>8.52</v>
+        <v>8.51</v>
       </c>
       <c r="D54" t="n">
         <v>0.18</v>
@@ -1325,7 +1325,7 @@
         <v>10960</v>
       </c>
       <c r="C56" t="n">
-        <v>10.7</v>
+        <v>10.68</v>
       </c>
       <c r="D56" t="n">
         <v>0.2</v>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13364</v>
+        <v>14440</v>
       </c>
       <c r="C59" t="n">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
       <c r="D59" t="n">
         <v>0.13</v>
@@ -1405,7 +1405,7 @@
         <v>659</v>
       </c>
       <c r="C61" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="D61" t="n">
         <v>0.03</v>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C62" t="n">
-        <v>8.33</v>
+        <v>8.34</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="63">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>540138</v>
+        <v>537721</v>
       </c>
       <c r="C65" t="n">
-        <v>19.75</v>
+        <v>18.34</v>
       </c>
       <c r="D65" t="n">
         <v>0.21</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>13364</v>
+        <v>14440</v>
       </c>
       <c r="C66" t="n">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
       <c r="D66" t="n">
         <v>0.13</v>
@@ -1565,7 +1565,7 @@
         <v>4099</v>
       </c>
       <c r="C71" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="D71" t="n">
         <v>0.26</v>
@@ -1581,7 +1581,7 @@
         <v>12182</v>
       </c>
       <c r="C72" t="n">
-        <v>7.49</v>
+        <v>7.48</v>
       </c>
       <c r="D72" t="n">
         <v>0.2</v>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13364</v>
+        <v>14440</v>
       </c>
       <c r="C80" t="n">
-        <v>10.84</v>
+        <v>10.73</v>
       </c>
       <c r="D80" t="n">
         <v>0.13</v>
@@ -1741,7 +1741,7 @@
         <v>18</v>
       </c>
       <c r="C82" t="n">
-        <v>5.66</v>
+        <v>5.65</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -1757,7 +1757,7 @@
         <v>7263</v>
       </c>
       <c r="C83" t="n">
-        <v>11.08</v>
+        <v>11.07</v>
       </c>
       <c r="D83" t="n">
         <v>0.05</v>
@@ -1869,7 +1869,7 @@
         <v>610</v>
       </c>
       <c r="C90" t="n">
-        <v>7.02</v>
+        <v>7.01</v>
       </c>
       <c r="D90" t="n">
         <v>0.14</v>
@@ -1901,7 +1901,7 @@
         <v>1562</v>
       </c>
       <c r="C92" t="n">
-        <v>16.16</v>
+        <v>16.15</v>
       </c>
       <c r="D92" t="n">
         <v>0.02</v>
@@ -1949,7 +1949,7 @@
         <v>4148</v>
       </c>
       <c r="C95" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="D95" t="n">
         <v>0.11</v>
@@ -1965,7 +1965,7 @@
         <v>13510</v>
       </c>
       <c r="C96" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="D96" t="n">
         <v>0.29</v>
@@ -1981,7 +1981,7 @@
         <v>328</v>
       </c>
       <c r="C97" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="D97" t="n">
         <v>0.8100000000000001</v>
@@ -1997,7 +1997,7 @@
         <v>51797</v>
       </c>
       <c r="C98" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
       <c r="D98" t="n">
         <v>0.3</v>
@@ -2045,7 +2045,7 @@
         <v>720</v>
       </c>
       <c r="C101" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
       <c r="D101" t="n">
         <v>0.03</v>
@@ -2141,7 +2141,7 @@
         <v>4580</v>
       </c>
       <c r="C107" t="n">
-        <v>7.47</v>
+        <v>7.46</v>
       </c>
       <c r="D107" t="n">
         <v>0.16</v>
@@ -2269,7 +2269,7 @@
         <v>1163</v>
       </c>
       <c r="C115" t="n">
-        <v>13.84</v>
+        <v>13.83</v>
       </c>
       <c r="D115" t="n">
         <v>0.02</v>
@@ -2285,7 +2285,7 @@
         <v>141180</v>
       </c>
       <c r="C116" t="n">
-        <v>11.15</v>
+        <v>10.95</v>
       </c>
       <c r="D116" t="n">
         <v>0.23</v>
@@ -2317,7 +2317,7 @@
         <v>1549</v>
       </c>
       <c r="C118" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="D118" t="n">
         <v>0.05</v>
@@ -2333,7 +2333,7 @@
         <v>610</v>
       </c>
       <c r="C119" t="n">
-        <v>6.94</v>
+        <v>6.93</v>
       </c>
       <c r="D119" t="n">
         <v>0.15</v>
@@ -2349,7 +2349,7 @@
         <v>966</v>
       </c>
       <c r="C120" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="D120" t="n">
         <v>0.13</v>
@@ -2362,13 +2362,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C121" t="n">
-        <v>10.42</v>
+        <v>10.41</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="122">
@@ -2429,7 +2429,7 @@
         <v>815</v>
       </c>
       <c r="C125" t="n">
-        <v>18.78</v>
+        <v>18.77</v>
       </c>
       <c r="D125" t="n">
         <v>0.02</v>
@@ -2445,7 +2445,7 @@
         <v>1305</v>
       </c>
       <c r="C126" t="n">
-        <v>8.390000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="D126" t="n">
         <v>0.22</v>
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>145382</v>
+        <v>144097</v>
       </c>
       <c r="C127" t="n">
-        <v>14.76</v>
+        <v>14.51</v>
       </c>
       <c r="D127" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="128">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>895</v>
+        <v>703</v>
       </c>
       <c r="C129" t="n">
         <v>15.99</v>
@@ -2509,7 +2509,7 @@
         <v>1268</v>
       </c>
       <c r="C130" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="D130" t="n">
         <v>0.06</v>
@@ -2541,7 +2541,7 @@
         <v>928</v>
       </c>
       <c r="C132" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="D132" t="n">
         <v>0.06</v>
@@ -2573,7 +2573,7 @@
         <v>2401</v>
       </c>
       <c r="C134" t="n">
-        <v>8.43</v>
+        <v>8.41</v>
       </c>
       <c r="D134" t="n">
         <v>0.22</v>
@@ -2589,7 +2589,7 @@
         <v>888</v>
       </c>
       <c r="C135" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
       <c r="D135" t="n">
         <v>0.12</v>
@@ -2685,7 +2685,7 @@
         <v>4159</v>
       </c>
       <c r="C141" t="n">
-        <v>12.01</v>
+        <v>12</v>
       </c>
       <c r="D141" t="n">
         <v>0.04</v>
@@ -2701,7 +2701,7 @@
         <v>818</v>
       </c>
       <c r="C142" t="n">
-        <v>6.96</v>
+        <v>6.95</v>
       </c>
       <c r="D142" t="n">
         <v>0.17</v>
@@ -2794,13 +2794,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>16</v>
+        <v>722</v>
       </c>
       <c r="C148" t="n">
-        <v>11.55</v>
+        <v>11.56</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="149">
@@ -2813,7 +2813,7 @@
         <v>26</v>
       </c>
       <c r="C149" t="n">
-        <v>5.67</v>
+        <v>5.66</v>
       </c>
       <c r="D149" t="n">
         <v>1</v>
@@ -2861,7 +2861,7 @@
         <v>774</v>
       </c>
       <c r="C152" t="n">
-        <v>6.95</v>
+        <v>6.94</v>
       </c>
       <c r="D152" t="n">
         <v>0.15</v>
@@ -2941,7 +2941,7 @@
         <v>4607</v>
       </c>
       <c r="C157" t="n">
-        <v>9.75</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D157" t="n">
         <v>0.15</v>
@@ -2970,13 +2970,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2792466</v>
+        <v>239181</v>
       </c>
       <c r="C159" t="n">
-        <v>52.77</v>
+        <v>68.14</v>
       </c>
       <c r="D159" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="160">
@@ -3021,7 +3021,7 @@
         <v>1663</v>
       </c>
       <c r="C162" t="n">
-        <v>10.93</v>
+        <v>10.92</v>
       </c>
       <c r="D162" t="n">
         <v>0.05</v>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>100260</v>
+        <v>102462</v>
       </c>
       <c r="C163" t="n">
-        <v>21.81</v>
+        <v>21.75</v>
       </c>
       <c r="D163" t="n">
         <v>0.06</v>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>13364</v>
+        <v>14440</v>
       </c>
       <c r="C165" t="n">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
       <c r="D165" t="n">
         <v>0.13</v>
@@ -3165,7 +3165,7 @@
         <v>758</v>
       </c>
       <c r="C171" t="n">
-        <v>6.95</v>
+        <v>6.94</v>
       </c>
       <c r="D171" t="n">
         <v>0.14</v>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>181265</v>
+        <v>182341</v>
       </c>
       <c r="C173" t="n">
-        <v>21.53</v>
+        <v>21.3</v>
       </c>
       <c r="D173" t="n">
         <v>0.09</v>
@@ -3213,7 +3213,7 @@
         <v>9149</v>
       </c>
       <c r="C174" t="n">
-        <v>13.48</v>
+        <v>13.47</v>
       </c>
       <c r="D174" t="n">
         <v>0.03</v>
@@ -3293,7 +3293,7 @@
         <v>1439</v>
       </c>
       <c r="C179" t="n">
-        <v>14.38</v>
+        <v>14.37</v>
       </c>
       <c r="D179" t="n">
         <v>0.04</v>
@@ -3309,7 +3309,7 @@
         <v>633</v>
       </c>
       <c r="C180" t="n">
-        <v>11.97</v>
+        <v>11.96</v>
       </c>
       <c r="D180" t="n">
         <v>0.03</v>
@@ -3373,7 +3373,7 @@
         <v>727</v>
       </c>
       <c r="C184" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="D184" t="n">
         <v>0.04</v>
@@ -3389,7 +3389,7 @@
         <v>4803</v>
       </c>
       <c r="C185" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
       <c r="D185" t="n">
         <v>0.16</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>13364</v>
+        <v>14440</v>
       </c>
       <c r="C190" t="n">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
       <c r="D190" t="n">
         <v>0.13</v>
@@ -3533,7 +3533,7 @@
         <v>154</v>
       </c>
       <c r="C194" t="n">
-        <v>11.29</v>
+        <v>11.28</v>
       </c>
       <c r="D194" t="n">
         <v>0.01</v>
@@ -3549,7 +3549,7 @@
         <v>113</v>
       </c>
       <c r="C195" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="D195" t="n">
         <v>0.01</v>
@@ -3581,7 +3581,7 @@
         <v>193</v>
       </c>
       <c r="C197" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="D197" t="n">
         <v>0.76</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>13364</v>
+        <v>14440</v>
       </c>
       <c r="C200" t="n">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
       <c r="D200" t="n">
         <v>0.13</v>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>26978</v>
+        <v>335182</v>
       </c>
       <c r="C201" t="n">
-        <v>7.1</v>
+        <v>63.53</v>
       </c>
       <c r="D201" t="n">
-        <v>0.92</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="202">
@@ -3677,7 +3677,7 @@
         <v>914</v>
       </c>
       <c r="C203" t="n">
-        <v>11.83</v>
+        <v>11.82</v>
       </c>
       <c r="D203" t="n">
         <v>0.04</v>
@@ -3693,7 +3693,7 @@
         <v>13702</v>
       </c>
       <c r="C204" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="D204" t="n">
         <v>0.26</v>
@@ -3709,7 +3709,7 @@
         <v>4766</v>
       </c>
       <c r="C205" t="n">
-        <v>7.5</v>
+        <v>7.49</v>
       </c>
       <c r="D205" t="n">
         <v>0.18</v>
@@ -3799,28 +3799,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1888.51</v>
+        <v>1957.28</v>
       </c>
       <c r="B2" t="n">
-        <v>9.212199999999999</v>
+        <v>9.547700000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>52.77</v>
+        <v>68.14</v>
       </c>
       <c r="D2" t="n">
         <v>5.63</v>
       </c>
       <c r="E2" t="n">
-        <v>4.445</v>
+        <v>6.4507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3071</v>
+        <v>0.3033</v>
       </c>
       <c r="G2" t="n">
         <v>0.1317</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3366</v>
+        <v>0.3415</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
